--- a/tests/fixtures/modeles/Modele_Nouveaux_Animaux.xlsx
+++ b/tests/fixtures/modeles/Modele_Nouveaux_Animaux.xlsx
@@ -35,7 +35,7 @@
     <t>Origine</t>
   </si>
   <si>
-    <t>Numéro EID complet (11 chiffres)</t>
+    <t>Numéro EID complet (11 ou 15 chiffres)</t>
   </si>
   <si>
     <t>Date d'entrée (JJ-MM-AAAA)</t>
@@ -59,7 +59,7 @@
     <t>née</t>
   </si>
   <si>
-    <t>16299151001</t>
+    <t>00000051001</t>
   </si>
   <si>
     <t>12-09-2026</t>
@@ -77,16 +77,16 @@
     <t>achetée</t>
   </si>
   <si>
-    <t>16480023987</t>
+    <t>00000123987</t>
   </si>
   <si>
     <t>03-01-2026</t>
   </si>
   <si>
-    <t>16299111042</t>
+    <t>00000011042</t>
   </si>
   <si>
-    <t>16352703253</t>
+    <t>00000203253</t>
   </si>
   <si>
     <t>↑ Exemple — à supprimer avant l'import.</t>
@@ -101,10 +101,10 @@
     <t>Numéro travail SIEOL (facultatif, format libre)</t>
   </si>
   <si>
-    <t>16401789234</t>
+    <t>00000189234</t>
   </si>
   <si>
-    <t>16512298877</t>
+    <t>00000298877</t>
   </si>
   <si>
     <t>05-09-2026</t>
@@ -125,7 +125,7 @@
     <t>Date (tri ou entrée) (JJ-MM-AAAA)</t>
   </si>
   <si>
-    <t>16299155102</t>
+    <t>00000055102</t>
   </si>
   <si>
     <t>01-09-2026</t>
@@ -137,7 +137,7 @@
     <t>55102</t>
   </si>
   <si>
-    <t>↑ Exemple : ligne 1 = agnelle née sur l'exploitation, mère identifiée par son numéro EID (11 chiffres) ; ligne 2 = agnelle achetée, père connu (bélier IA, identifié pareil par son numéro EID). À supprimer avant l'import.</t>
+    <t>↑ Exemple : ligne 1 = agnelle née sur l'exploitation, mère identifiée par son numéro EID (11 ou 15 chiffres) ; ligne 2 = agnelle achetée, père connu (bélier IA, identifié pareil par son numéro EID). À supprimer avant l'import.</t>
   </si>
   <si>
     <t>À quoi sert ce fichier</t>
@@ -158,7 +158,7 @@
     <t>Origine — "née" (née sur l'exploitation) ou "achetée". Liste déroulante en place, disponible sur les 3 onglets.</t>
   </si>
   <si>
-    <t>Père / Mère — facultatifs sur les 3 onglets, surtout utiles en cas d'achat. Toujours le numéro EID (11 chiffres) de l'animal, pas le numéro officiel à 5 chiffres (pas assez unique) ni un nom. Si ce numéro correspond à un animal déjà connu dans Ovilog, la fiche est automatiquement rattachée (lien cliquable) ; sinon la valeur est gardée telle quelle, en attente que cet animal soit lui-même importé un jour.</t>
+    <t>Père / Mère — facultatifs sur les 3 onglets, surtout utiles en cas d'achat. Toujours le numéro EID (11 ou 15 chiffres) de l'animal, pas le numéro officiel à 5 chiffres (pas assez unique) ni un nom. Si ce numéro correspond à un animal déjà connu dans Ovilog, la fiche est automatiquement rattachée (lien cliquable) ; sinon la valeur est gardée telle quelle, en attente que cet animal soit lui-même importé un jour.</t>
   </si>
   <si>
     <t>Statut (onglets Brebis et Béliers)</t>
